--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\proyect exitoso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3DCB48-D366-450C-AFBB-62E66A348252}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEAAC668-9FF8-4E08-937A-2AEAF43D4472}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>23CODE RECORDS</t>
   </si>
@@ -35,6 +35,12 @@
   </si>
   <si>
     <t>CARLOS GOMEZ BOLERO</t>
+  </si>
+  <si>
+    <t>MARIA PEREZ SUNIGA</t>
+  </si>
+  <si>
+    <t>ANGELO FERRERO</t>
   </si>
 </sst>
 </file>
@@ -114,13 +120,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -432,11 +438,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -453,11 +459,33 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="2">
+        <v>3124879654</v>
+      </c>
+      <c r="C3" s="2">
+        <v>101135648</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>3014458719</v>
+      </c>
+      <c r="C4">
+        <v>12329591</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
         <v>3229127539</v>
       </c>
-      <c r="C3" s="4">
-        <v>101135648</v>
+      <c r="C5">
+        <v>89392929</v>
       </c>
     </row>
   </sheetData>

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\proyect exitoso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEAAC668-9FF8-4E08-937A-2AEAF43D4472}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591D95F9-850D-49FD-8EA2-E13F3ABEBC76}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
   <si>
     <t>23CODE RECORDS</t>
   </si>
@@ -34,20 +34,1571 @@
     <t>Número de Documento</t>
   </si>
   <si>
-    <t>CARLOS GOMEZ BOLERO</t>
-  </si>
-  <si>
-    <t>MARIA PEREZ SUNIGA</t>
-  </si>
-  <si>
     <t>ANGELO FERRERO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL JIMENEZ GIRALDO</t>
+  </si>
+  <si>
+    <t>3229120006</t>
+  </si>
+  <si>
+    <t>1116242193</t>
+  </si>
+  <si>
+    <t>VALERY MICHELL SANCHEZ ABELLA</t>
+  </si>
+  <si>
+    <t>3229120009</t>
+  </si>
+  <si>
+    <t>1082155955</t>
+  </si>
+  <si>
+    <t>FREDY EDUARDO LOPEZ GARZON</t>
+  </si>
+  <si>
+    <t>3229120010</t>
+  </si>
+  <si>
+    <t>79994034</t>
+  </si>
+  <si>
+    <t>JAMILTON TRUJILLO DELGADO</t>
+  </si>
+  <si>
+    <t>3229120013</t>
+  </si>
+  <si>
+    <t>1129004882</t>
+  </si>
+  <si>
+    <t>KEVIN FELIPE TRUJILLO GARZON</t>
+  </si>
+  <si>
+    <t>3229120015</t>
+  </si>
+  <si>
+    <t>1007605056</t>
+  </si>
+  <si>
+    <t>3229120007</t>
+  </si>
+  <si>
+    <t>5389299</t>
+  </si>
+  <si>
+    <t>LUDY ROJAS RAMIREZ</t>
+  </si>
+  <si>
+    <t>3229120025</t>
+  </si>
+  <si>
+    <t>40613498</t>
+  </si>
+  <si>
+    <t>DIANA MILENA FIGUEROA BONILLA</t>
+  </si>
+  <si>
+    <t>3229120022</t>
+  </si>
+  <si>
+    <t>55117980</t>
+  </si>
+  <si>
+    <t>PAOLA ANDREA SANTOS OBREGON</t>
+  </si>
+  <si>
+    <t>3229120028</t>
+  </si>
+  <si>
+    <t>1004301446</t>
+  </si>
+  <si>
+    <t>MARIA CONSTANZA RINCON FOMEQUE</t>
+  </si>
+  <si>
+    <t>3229120036</t>
+  </si>
+  <si>
+    <t>1077856212</t>
+  </si>
+  <si>
+    <t>CARLOS DANIEL BONILLA CORREDOR</t>
+  </si>
+  <si>
+    <t>3229120040</t>
+  </si>
+  <si>
+    <t>1015480567</t>
+  </si>
+  <si>
+    <t>LUIS ORLANDO CELIS GOMEZ</t>
+  </si>
+  <si>
+    <t>3229120043</t>
+  </si>
+  <si>
+    <t>91041934</t>
+  </si>
+  <si>
+    <t>ANDRES FELIPE SALAZAR DURAN</t>
+  </si>
+  <si>
+    <t>3229120047</t>
+  </si>
+  <si>
+    <t>1117484767</t>
+  </si>
+  <si>
+    <t>NATALIA ANDREA CAMPO ESCOBAR</t>
+  </si>
+  <si>
+    <t>3229120051</t>
+  </si>
+  <si>
+    <t>1096212003</t>
+  </si>
+  <si>
+    <t>JAVIER GALVAN CASTELLANOS</t>
+  </si>
+  <si>
+    <t>3229120057</t>
+  </si>
+  <si>
+    <t>91295051</t>
+  </si>
+  <si>
+    <t>CEIL QUINTERO ROJAS</t>
+  </si>
+  <si>
+    <t>3229120058</t>
+  </si>
+  <si>
+    <t>55216169</t>
+  </si>
+  <si>
+    <t>HEMERSON JOSE HERNANDEZ CARRANZA</t>
+  </si>
+  <si>
+    <t>3229120059</t>
+  </si>
+  <si>
+    <t>1081760795</t>
+  </si>
+  <si>
+    <t>LUZ DARY ROSAS GAMBINDO</t>
+  </si>
+  <si>
+    <t>3229120068</t>
+  </si>
+  <si>
+    <t>46682570</t>
+  </si>
+  <si>
+    <t>MISAEL CESPEDES RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>3229120070</t>
+  </si>
+  <si>
+    <t>79528392</t>
+  </si>
+  <si>
+    <t>ANA CECILIA VELASQUEZ GUZMAN</t>
+  </si>
+  <si>
+    <t>3229120063</t>
+  </si>
+  <si>
+    <t>31857408</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIAN TORRES SANCHEZ</t>
+  </si>
+  <si>
+    <t>3229120071</t>
+  </si>
+  <si>
+    <t>1144096977</t>
+  </si>
+  <si>
+    <t>LEONARDO ANGARITA BERMUDEZ</t>
+  </si>
+  <si>
+    <t>3229120074</t>
+  </si>
+  <si>
+    <t>77186854</t>
+  </si>
+  <si>
+    <t>YURLADIS ESTHER MEDINA ROMO</t>
+  </si>
+  <si>
+    <t>3229120075</t>
+  </si>
+  <si>
+    <t>1081761800</t>
+  </si>
+  <si>
+    <t>ANA SOFIA CASTAÑO ZAPATA</t>
+  </si>
+  <si>
+    <t>3229120078</t>
+  </si>
+  <si>
+    <t>1057095885</t>
+  </si>
+  <si>
+    <t>VICTOR FERNANDO GUEVARA GUERRERO</t>
+  </si>
+  <si>
+    <t>3229120081</t>
+  </si>
+  <si>
+    <t>1121846872</t>
+  </si>
+  <si>
+    <t>ALEXANDER TELLO TRIANA</t>
+  </si>
+  <si>
+    <t>3229120085</t>
+  </si>
+  <si>
+    <t>94487266</t>
+  </si>
+  <si>
+    <t>PEDRO URIEL MARTHA</t>
+  </si>
+  <si>
+    <t>3229120086</t>
+  </si>
+  <si>
+    <t>19179622</t>
+  </si>
+  <si>
+    <t>ERICA SANCHEZ GUZMAN</t>
+  </si>
+  <si>
+    <t>3229120089</t>
+  </si>
+  <si>
+    <t>52194836</t>
+  </si>
+  <si>
+    <t>JHON MARIO GUZMAN MAHECHA</t>
+  </si>
+  <si>
+    <t>3229120099</t>
+  </si>
+  <si>
+    <t>1110581533</t>
+  </si>
+  <si>
+    <t>SAUL PONGUTA RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>3229120094</t>
+  </si>
+  <si>
+    <t>74362037</t>
+  </si>
+  <si>
+    <t>ALBENY MENESES</t>
+  </si>
+  <si>
+    <t>3229120101</t>
+  </si>
+  <si>
+    <t>36346248</t>
+  </si>
+  <si>
+    <t>EMANUEL DAVID FUQUENE SANABRIA</t>
+  </si>
+  <si>
+    <t>3229120098</t>
+  </si>
+  <si>
+    <t>1012332355</t>
+  </si>
+  <si>
+    <t>JUAN PABLO HERNANDEZ TRUJILLO</t>
+  </si>
+  <si>
+    <t>3229120108</t>
+  </si>
+  <si>
+    <t>1006089464</t>
+  </si>
+  <si>
+    <t>EDUARD LEONARDO AQUINO ESTEVES</t>
+  </si>
+  <si>
+    <t>3229120109</t>
+  </si>
+  <si>
+    <t>1246228444</t>
+  </si>
+  <si>
+    <t>3229120106</t>
+  </si>
+  <si>
+    <t>1120365182</t>
+  </si>
+  <si>
+    <t>BELSI DEL CARMEN PEREZ PULGARIN</t>
+  </si>
+  <si>
+    <t>3229120125</t>
+  </si>
+  <si>
+    <t>31402274</t>
+  </si>
+  <si>
+    <t>3229120123</t>
+  </si>
+  <si>
+    <t>1123810083</t>
+  </si>
+  <si>
+    <t>JAIRO ALBERTO CASTILLO NIETO</t>
+  </si>
+  <si>
+    <t>3229120132</t>
+  </si>
+  <si>
+    <t>1021397904</t>
+  </si>
+  <si>
+    <t>SAMUEL ALFREDO CASTILLO GUARAMA</t>
+  </si>
+  <si>
+    <t>3229120142</t>
+  </si>
+  <si>
+    <t>1030523293</t>
+  </si>
+  <si>
+    <t>3229120126</t>
+  </si>
+  <si>
+    <t>51695471</t>
+  </si>
+  <si>
+    <t>DIANA ANDREA PALENCIA TRIANA</t>
+  </si>
+  <si>
+    <t>3229120148</t>
+  </si>
+  <si>
+    <t>35531302</t>
+  </si>
+  <si>
+    <t>MELISSA MARIN GIRALDO</t>
+  </si>
+  <si>
+    <t>3229120171</t>
+  </si>
+  <si>
+    <t>1060656914</t>
+  </si>
+  <si>
+    <t>NATALIA GUZMAN HOYOS</t>
+  </si>
+  <si>
+    <t>3229120172</t>
+  </si>
+  <si>
+    <t>1067286330</t>
+  </si>
+  <si>
+    <t>SAMUEL DAVID CERA MONTENEGRO</t>
+  </si>
+  <si>
+    <t>3229120174</t>
+  </si>
+  <si>
+    <t>1085107755</t>
+  </si>
+  <si>
+    <t>3229120164</t>
+  </si>
+  <si>
+    <t>1120366631</t>
+  </si>
+  <si>
+    <t>CLAUDIA RIAÑO SALAZAR</t>
+  </si>
+  <si>
+    <t>3229120165</t>
+  </si>
+  <si>
+    <t>35534412</t>
+  </si>
+  <si>
+    <t>MARIA LIBRADA TRIANA HERRERA</t>
+  </si>
+  <si>
+    <t>3229120177</t>
+  </si>
+  <si>
+    <t>41547594</t>
+  </si>
+  <si>
+    <t>AMPARO POLOCHE CHANGO</t>
+  </si>
+  <si>
+    <t>3229120178</t>
+  </si>
+  <si>
+    <t>30312059</t>
+  </si>
+  <si>
+    <t>FERNANDO JOSE PALLARES BARRIOS</t>
+  </si>
+  <si>
+    <t>3229120179</t>
+  </si>
+  <si>
+    <t>1085105516</t>
+  </si>
+  <si>
+    <t>MARIA CAMILA BEDOYA GARCIA</t>
+  </si>
+  <si>
+    <t>3229120181</t>
+  </si>
+  <si>
+    <t>1115182717</t>
+  </si>
+  <si>
+    <t>ALFONSO PINCHAO NARVAEZ</t>
+  </si>
+  <si>
+    <t>3229120182</t>
+  </si>
+  <si>
+    <t>5258836</t>
+  </si>
+  <si>
+    <t>CARLOS ANDRES RUIZ ROJAS</t>
+  </si>
+  <si>
+    <t>3229120188</t>
+  </si>
+  <si>
+    <t>7701568</t>
+  </si>
+  <si>
+    <t>ENRIQUE VALENCIA SIERRA</t>
+  </si>
+  <si>
+    <t>3229120190</t>
+  </si>
+  <si>
+    <t>91321810</t>
+  </si>
+  <si>
+    <t>3229120183</t>
+  </si>
+  <si>
+    <t>1116502831</t>
+  </si>
+  <si>
+    <t>HERNANDO ARTURO BETTS RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>3229120194</t>
+  </si>
+  <si>
+    <t>1140873700</t>
+  </si>
+  <si>
+    <t>JULIAN ANDRES VARELA RIAÑO</t>
+  </si>
+  <si>
+    <t>3229120198</t>
+  </si>
+  <si>
+    <t>80209142</t>
+  </si>
+  <si>
+    <t>3229120197</t>
+  </si>
+  <si>
+    <t>1089932629</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA RAMIREZ SANDOVAL</t>
+  </si>
+  <si>
+    <t>3229120199</t>
+  </si>
+  <si>
+    <t>1094221251</t>
+  </si>
+  <si>
+    <t>JOAN SEBASTIAN OSPINA LABRADOR</t>
+  </si>
+  <si>
+    <t>3229120223</t>
+  </si>
+  <si>
+    <t>1006123287</t>
+  </si>
+  <si>
+    <t>KENNETH JOHAN MORENO ORTEGA</t>
+  </si>
+  <si>
+    <t>3229120225</t>
+  </si>
+  <si>
+    <t>1085105272</t>
+  </si>
+  <si>
+    <t>3229120203</t>
+  </si>
+  <si>
+    <t>1140921735</t>
+  </si>
+  <si>
+    <t>SANTIAGO JOSE OROZCO OSPINO</t>
+  </si>
+  <si>
+    <t>3229120232</t>
+  </si>
+  <si>
+    <t>1043137995</t>
+  </si>
+  <si>
+    <t>NORBERTO GAMBOA BECERRA</t>
+  </si>
+  <si>
+    <t>3229120234</t>
+  </si>
+  <si>
+    <t>79053267</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO TRUJILLO GOMEZ</t>
+  </si>
+  <si>
+    <t>3229120240</t>
+  </si>
+  <si>
+    <t>93366602</t>
+  </si>
+  <si>
+    <t>YARI YURENI CRUZ NIETO</t>
+  </si>
+  <si>
+    <t>3229120254</t>
+  </si>
+  <si>
+    <t>1006155221</t>
+  </si>
+  <si>
+    <t>JAVIER ENRIQUE LOPEZ QUINTERO</t>
+  </si>
+  <si>
+    <t>3229120255</t>
+  </si>
+  <si>
+    <t>1067817586</t>
+  </si>
+  <si>
+    <t>LEIDY MARCELA FAJARDO TIQUE</t>
+  </si>
+  <si>
+    <t>3229120259</t>
+  </si>
+  <si>
+    <t>1030609574</t>
+  </si>
+  <si>
+    <t>MARLEIDY VEGA YATE</t>
+  </si>
+  <si>
+    <t>3229120262</t>
+  </si>
+  <si>
+    <t>1006156298</t>
+  </si>
+  <si>
+    <t>LIBARDO SARMIENTO GOMEZ</t>
+  </si>
+  <si>
+    <t>3229120265</t>
+  </si>
+  <si>
+    <t>5581216</t>
+  </si>
+  <si>
+    <t>3229120248</t>
+  </si>
+  <si>
+    <t>1244553</t>
+  </si>
+  <si>
+    <t>NELLY DEL CARMEN CABRERA MONTESINO</t>
+  </si>
+  <si>
+    <t>3229120290</t>
+  </si>
+  <si>
+    <t>51983833</t>
+  </si>
+  <si>
+    <t>LAURA MARCELA RINCON</t>
+  </si>
+  <si>
+    <t>3229120279</t>
+  </si>
+  <si>
+    <t>63533664</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIAN LOPEZ CHACON</t>
+  </si>
+  <si>
+    <t>3229120308</t>
+  </si>
+  <si>
+    <t>1010193562</t>
+  </si>
+  <si>
+    <t>EUDORO ALBERTO VACAREZ VARGAS</t>
+  </si>
+  <si>
+    <t>3229120302</t>
+  </si>
+  <si>
+    <t>1118531294</t>
+  </si>
+  <si>
+    <t>FREDDY ALEXIS CEDEÑO FLOREZ</t>
+  </si>
+  <si>
+    <t>3229120312</t>
+  </si>
+  <si>
+    <t>17595213</t>
+  </si>
+  <si>
+    <t>MILED SAMIRIS CALVO MONTERO</t>
+  </si>
+  <si>
+    <t>3229120322</t>
+  </si>
+  <si>
+    <t>1081758060</t>
+  </si>
+  <si>
+    <t>ANA ROCIO RISCANEVO TUNAROZA</t>
+  </si>
+  <si>
+    <t>3229120325</t>
+  </si>
+  <si>
+    <t>1007519409</t>
+  </si>
+  <si>
+    <t>CAMPO ELIAS OJEDA FORERO</t>
+  </si>
+  <si>
+    <t>3229120335</t>
+  </si>
+  <si>
+    <t>79217267</t>
+  </si>
+  <si>
+    <t>ANDRES LEONARDO LOPEZ CORONADO</t>
+  </si>
+  <si>
+    <t>3229120337</t>
+  </si>
+  <si>
+    <t>1030622948</t>
+  </si>
+  <si>
+    <t>WILSON ORLANDO LOPEZ BARRAGAN</t>
+  </si>
+  <si>
+    <t>3229120341</t>
+  </si>
+  <si>
+    <t>11255998</t>
+  </si>
+  <si>
+    <t>JOHN JAMES MARMOLEJO CASTRO</t>
+  </si>
+  <si>
+    <t>3229120350</t>
+  </si>
+  <si>
+    <t>1110284685</t>
+  </si>
+  <si>
+    <t>3229120330</t>
+  </si>
+  <si>
+    <t>1021683361</t>
+  </si>
+  <si>
+    <t>FRANCEL MAURICIO LEGUIZAMON GUERRA</t>
+  </si>
+  <si>
+    <t>3229120388</t>
+  </si>
+  <si>
+    <t>79925413</t>
+  </si>
+  <si>
+    <t>ROINEL DAVID CALVO DE LA HOZ</t>
+  </si>
+  <si>
+    <t>3229120391</t>
+  </si>
+  <si>
+    <t>1007162367</t>
+  </si>
+  <si>
+    <t>JOSE RICARDO OLIVAR BOLAÑOS</t>
+  </si>
+  <si>
+    <t>3229120395</t>
+  </si>
+  <si>
+    <t>1005718311</t>
+  </si>
+  <si>
+    <t>MILEIDI VIVIANA MARTINEZ AYALA</t>
+  </si>
+  <si>
+    <t>3229120398</t>
+  </si>
+  <si>
+    <t>1116814240</t>
+  </si>
+  <si>
+    <t>3229120382</t>
+  </si>
+  <si>
+    <t>1142717405</t>
+  </si>
+  <si>
+    <t>JULIAN CAMILO SERNA MARTINEZ</t>
+  </si>
+  <si>
+    <t>3229120423</t>
+  </si>
+  <si>
+    <t>1041229728</t>
+  </si>
+  <si>
+    <t>LUIS ADILIO BONILLA QUINTERO</t>
+  </si>
+  <si>
+    <t>3229120422</t>
+  </si>
+  <si>
+    <t>6613451</t>
+  </si>
+  <si>
+    <t>3229120403</t>
+  </si>
+  <si>
+    <t>1029400248</t>
+  </si>
+  <si>
+    <t>MARTHA JOHANA MONROY REYES</t>
+  </si>
+  <si>
+    <t>3229120424</t>
+  </si>
+  <si>
+    <t>1070620085</t>
+  </si>
+  <si>
+    <t>SEBASTIAN RODRIGUEZ PIEDRAHITA</t>
+  </si>
+  <si>
+    <t>3229120427</t>
+  </si>
+  <si>
+    <t>1058198402</t>
+  </si>
+  <si>
+    <t>ANA VICTORIA CASTILLO CASTRO</t>
+  </si>
+  <si>
+    <t>3229120432</t>
+  </si>
+  <si>
+    <t>1090413233</t>
+  </si>
+  <si>
+    <t>JUAN ESTEBAN SOLER RUIZ</t>
+  </si>
+  <si>
+    <t>3229120436</t>
+  </si>
+  <si>
+    <t>1001273479</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO ESTUPIÑAN</t>
+  </si>
+  <si>
+    <t>3229120450</t>
+  </si>
+  <si>
+    <t>1094243891</t>
+  </si>
+  <si>
+    <t>3229120435</t>
+  </si>
+  <si>
+    <t>1053340672</t>
+  </si>
+  <si>
+    <t>3229120460</t>
+  </si>
+  <si>
+    <t>1092538531</t>
+  </si>
+  <si>
+    <t>YESICA ALEJANDRA RIVERA CASTILLO</t>
+  </si>
+  <si>
+    <t>3229120465</t>
+  </si>
+  <si>
+    <t>1006446698</t>
+  </si>
+  <si>
+    <t>ZULMA YULIETH REYES PAEZ</t>
+  </si>
+  <si>
+    <t>3229120468</t>
+  </si>
+  <si>
+    <t>1006446763</t>
+  </si>
+  <si>
+    <t>LORENA PATRICIA RAMIREZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>3229120471</t>
+  </si>
+  <si>
+    <t>39582582</t>
+  </si>
+  <si>
+    <t>FREDY ARTURO PAEZ MARTINEZ</t>
+  </si>
+  <si>
+    <t>3229120474</t>
+  </si>
+  <si>
+    <t>1001064678</t>
+  </si>
+  <si>
+    <t>INGRID DANIELA FLORES FERNANDEZ</t>
+  </si>
+  <si>
+    <t>3229120477</t>
+  </si>
+  <si>
+    <t>1006449364</t>
+  </si>
+  <si>
+    <t>LUISA FERNANDA FORERO HURTADO</t>
+  </si>
+  <si>
+    <t>3229120480</t>
+  </si>
+  <si>
+    <t>1032455683</t>
+  </si>
+  <si>
+    <t>NELLY ESPERANZA RUBIO MOTTA</t>
+  </si>
+  <si>
+    <t>3229120488</t>
+  </si>
+  <si>
+    <t>53131370</t>
+  </si>
+  <si>
+    <t>JOHAN ALEXANDER MARTINEZ LOMBANA</t>
+  </si>
+  <si>
+    <t>3229120491</t>
+  </si>
+  <si>
+    <t>1073162758</t>
+  </si>
+  <si>
+    <t>FERNANDO SAAVEDRA VIAFARA</t>
+  </si>
+  <si>
+    <t>3229120495</t>
+  </si>
+  <si>
+    <t>6320694</t>
+  </si>
+  <si>
+    <t>CESAR EMILIO BALMACEDA LOPEZ</t>
+  </si>
+  <si>
+    <t>3229120498</t>
+  </si>
+  <si>
+    <t>1006457251</t>
+  </si>
+  <si>
+    <t>NOHORA CECILIA CUBIDES CASTRO</t>
+  </si>
+  <si>
+    <t>3229120509</t>
+  </si>
+  <si>
+    <t>51629108</t>
+  </si>
+  <si>
+    <t>3229120510</t>
+  </si>
+  <si>
+    <t>1097498756</t>
+  </si>
+  <si>
+    <t>JUAN DANIEL ALGARIN CANTILLO</t>
+  </si>
+  <si>
+    <t>3229120511</t>
+  </si>
+  <si>
+    <t>1111668377</t>
+  </si>
+  <si>
+    <t>YOAN FERSON ANIMERO SALAZAR</t>
+  </si>
+  <si>
+    <t>3229120516</t>
+  </si>
+  <si>
+    <t>1006158582</t>
+  </si>
+  <si>
+    <t>JAIRO ALEXANDER GARCIA CASALLAS</t>
+  </si>
+  <si>
+    <t>3229120528</t>
+  </si>
+  <si>
+    <t>1020736564</t>
+  </si>
+  <si>
+    <t>3229120501</t>
+  </si>
+  <si>
+    <t>1072665227</t>
+  </si>
+  <si>
+    <t>CAROLINA GONZALEZ TOBON</t>
+  </si>
+  <si>
+    <t>3229120530</t>
+  </si>
+  <si>
+    <t>1011324541</t>
+  </si>
+  <si>
+    <t>YURANY ZULUAGA ZULUAGA</t>
+  </si>
+  <si>
+    <t>3229120536</t>
+  </si>
+  <si>
+    <t>1014238807</t>
+  </si>
+  <si>
+    <t>OLGA JEANETTE BONILLA LEON</t>
+  </si>
+  <si>
+    <t>3229120533</t>
+  </si>
+  <si>
+    <t>1024473618</t>
+  </si>
+  <si>
+    <t>MARIA YERLY CALDERON SALCEDO</t>
+  </si>
+  <si>
+    <t>3229120541</t>
+  </si>
+  <si>
+    <t>55068353</t>
+  </si>
+  <si>
+    <t>LUIS RAUL BRUGES BASTOS</t>
+  </si>
+  <si>
+    <t>3229120558</t>
+  </si>
+  <si>
+    <t>88240882</t>
+  </si>
+  <si>
+    <t>3229120552</t>
+  </si>
+  <si>
+    <t>1022966528</t>
+  </si>
+  <si>
+    <t>ROSA NELVA ARERO SALAZAR</t>
+  </si>
+  <si>
+    <t>3229120564</t>
+  </si>
+  <si>
+    <t>51588147</t>
+  </si>
+  <si>
+    <t>3229120560</t>
+  </si>
+  <si>
+    <t>4484752</t>
+  </si>
+  <si>
+    <t>CAMILA ALEJANDRA CUERVO HERRERA</t>
+  </si>
+  <si>
+    <t>3229120575</t>
+  </si>
+  <si>
+    <t>1023035924</t>
+  </si>
+  <si>
+    <t>GUZMAN DIAZ PAEZ</t>
+  </si>
+  <si>
+    <t>3229120570</t>
+  </si>
+  <si>
+    <t>1093923841</t>
+  </si>
+  <si>
+    <t>MARTHA RUBIELA ALVAREZ</t>
+  </si>
+  <si>
+    <t>3229120588</t>
+  </si>
+  <si>
+    <t>41917575</t>
+  </si>
+  <si>
+    <t>LISNEIRA MARIA TORRES OLAYA</t>
+  </si>
+  <si>
+    <t>3229120593</t>
+  </si>
+  <si>
+    <t>1044421125</t>
+  </si>
+  <si>
+    <t>ROCIO DEL CARMEN MARTINEZ CARDONA</t>
+  </si>
+  <si>
+    <t>3229120590</t>
+  </si>
+  <si>
+    <t>51801312</t>
+  </si>
+  <si>
+    <t>ANGIE GABRIELA BURGOS RAMIREZ</t>
+  </si>
+  <si>
+    <t>3229120600</t>
+  </si>
+  <si>
+    <t>1093589475</t>
+  </si>
+  <si>
+    <t>OMAR WILLIAM GONZALEZ GUZMAN</t>
+  </si>
+  <si>
+    <t>3229120594</t>
+  </si>
+  <si>
+    <t>11524608</t>
+  </si>
+  <si>
+    <t>DIANA LISBETH DUARTE RUBIANO</t>
+  </si>
+  <si>
+    <t>3229120603</t>
+  </si>
+  <si>
+    <t>1070308288</t>
+  </si>
+  <si>
+    <t>JORGE ANGELO NARVAEZ</t>
+  </si>
+  <si>
+    <t>3229120613</t>
+  </si>
+  <si>
+    <t>12125742</t>
+  </si>
+  <si>
+    <t>PABLO LUIS CASTAÑEDA ANAYA</t>
+  </si>
+  <si>
+    <t>3229120615</t>
+  </si>
+  <si>
+    <t>78301805</t>
+  </si>
+  <si>
+    <t>GLORIA PATRICIA VANEGAS OSTOS</t>
+  </si>
+  <si>
+    <t>3229120616</t>
+  </si>
+  <si>
+    <t>20831116</t>
+  </si>
+  <si>
+    <t>RUBIELA RODRIGUEZ MONROY</t>
+  </si>
+  <si>
+    <t>3229120627</t>
+  </si>
+  <si>
+    <t>52364854</t>
+  </si>
+  <si>
+    <t>CONSTANTINO MERLO GONZALEZ</t>
+  </si>
+  <si>
+    <t>3229120621</t>
+  </si>
+  <si>
+    <t>74081114</t>
+  </si>
+  <si>
+    <t>GUILLERMO ANAYA GUERRERO</t>
+  </si>
+  <si>
+    <t>3229120637</t>
+  </si>
+  <si>
+    <t>85442494</t>
+  </si>
+  <si>
+    <t>JAVIER GOMEZ RINCON</t>
+  </si>
+  <si>
+    <t>3229120641</t>
+  </si>
+  <si>
+    <t>79812916</t>
+  </si>
+  <si>
+    <t>ASTRID OFELIA ALFONSO JUSTINICO</t>
+  </si>
+  <si>
+    <t>3229120645</t>
+  </si>
+  <si>
+    <t>1007781806</t>
+  </si>
+  <si>
+    <t>LICETH VALENTINA ARAGON RIVADENEIRA</t>
+  </si>
+  <si>
+    <t>3229120650</t>
+  </si>
+  <si>
+    <t>1105675792</t>
+  </si>
+  <si>
+    <t>3229120628</t>
+  </si>
+  <si>
+    <t>8242169</t>
+  </si>
+  <si>
+    <t>SEBASTIAN URIETA BARAHONA</t>
+  </si>
+  <si>
+    <t>3229120654</t>
+  </si>
+  <si>
+    <t>1031120147</t>
+  </si>
+  <si>
+    <t>LOLY YASMIN CUERVO CARDENAS</t>
+  </si>
+  <si>
+    <t>3229120659</t>
+  </si>
+  <si>
+    <t>52448266</t>
+  </si>
+  <si>
+    <t>CRISTIAN GERMAN RODRIGUEZ MORENO</t>
+  </si>
+  <si>
+    <t>3229120663</t>
+  </si>
+  <si>
+    <t>1010118541</t>
+  </si>
+  <si>
+    <t>ANY GERALDINE PACHON CASTRO</t>
+  </si>
+  <si>
+    <t>3229120667</t>
+  </si>
+  <si>
+    <t>1010157108</t>
+  </si>
+  <si>
+    <t>ANTONIO MARIA PALLARE DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>3229120672</t>
+  </si>
+  <si>
+    <t>7599696</t>
+  </si>
+  <si>
+    <t>ALFONSO SOCHA GARRIDO</t>
+  </si>
+  <si>
+    <t>3229120676</t>
+  </si>
+  <si>
+    <t>19460440</t>
+  </si>
+  <si>
+    <t>DIEGO ORLANDO GOMEZ APONTE</t>
+  </si>
+  <si>
+    <t>3229120678</t>
+  </si>
+  <si>
+    <t>1014184927</t>
+  </si>
+  <si>
+    <t>3229120665</t>
+  </si>
+  <si>
+    <t>1023379374</t>
+  </si>
+  <si>
+    <t>JESUS ELIAS CELIS PIÑA</t>
+  </si>
+  <si>
+    <t>3229120675</t>
+  </si>
+  <si>
+    <t>1090531673</t>
+  </si>
+  <si>
+    <t>FELIX ANTONIO MARTINEZ DIAZ</t>
+  </si>
+  <si>
+    <t>3229120680</t>
+  </si>
+  <si>
+    <t>80380800</t>
+  </si>
+  <si>
+    <t>GREIS CAROLINA PARRA TOVAR</t>
+  </si>
+  <si>
+    <t>3229120681</t>
+  </si>
+  <si>
+    <t>1048441107</t>
+  </si>
+  <si>
+    <t>MARIA ENCY LOPEZ PALACIOS</t>
+  </si>
+  <si>
+    <t>3229120686</t>
+  </si>
+  <si>
+    <t>54252648</t>
+  </si>
+  <si>
+    <t>CARLOS ANDRES SALCEDO BENAVIDES</t>
+  </si>
+  <si>
+    <t>3229120695</t>
+  </si>
+  <si>
+    <t>1002302584</t>
+  </si>
+  <si>
+    <t>MARISOL SARMIENTO SARMIENTO</t>
+  </si>
+  <si>
+    <t>3229120691</t>
+  </si>
+  <si>
+    <t>1071143542</t>
+  </si>
+  <si>
+    <t>MONICA ALEJANDRA JIMENEZ ÑUSTES</t>
+  </si>
+  <si>
+    <t>3229120697</t>
+  </si>
+  <si>
+    <t>1000618485</t>
+  </si>
+  <si>
+    <t>RUSBY YALILE MALAGON RUIZ</t>
+  </si>
+  <si>
+    <t>3229120699</t>
+  </si>
+  <si>
+    <t>52557137</t>
+  </si>
+  <si>
+    <t>MELANY MIRIT RODRIGUEZ AGUILAR</t>
+  </si>
+  <si>
+    <t>3229120702</t>
+  </si>
+  <si>
+    <t>1128165938</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO AMAYA SALAZAR</t>
+  </si>
+  <si>
+    <t>3229120705</t>
+  </si>
+  <si>
+    <t>9526156</t>
+  </si>
+  <si>
+    <t>ROMEL MAURICIO BRAVO MUÑOZ</t>
+  </si>
+  <si>
+    <t>3229120709</t>
+  </si>
+  <si>
+    <t>4666967</t>
+  </si>
+  <si>
+    <t>GLORIA ESPERANZA JARAMILLO VASQUEZ</t>
+  </si>
+  <si>
+    <t>3229120710</t>
+  </si>
+  <si>
+    <t>42902818</t>
+  </si>
+  <si>
+    <t>3229120704</t>
+  </si>
+  <si>
+    <t>1021684163</t>
+  </si>
+  <si>
+    <t>EDWIN GIOVANNI LOPEZ TORRES</t>
+  </si>
+  <si>
+    <t>3229120713</t>
+  </si>
+  <si>
+    <t>7183790</t>
+  </si>
+  <si>
+    <t>MAGDA LORENA ESLAVA RUEDAS</t>
+  </si>
+  <si>
+    <t>3229120717</t>
+  </si>
+  <si>
+    <t>60385003</t>
+  </si>
+  <si>
+    <t>DIEGO ALEJANDRO SANGUINO PEREZ</t>
+  </si>
+  <si>
+    <t>3229120720</t>
+  </si>
+  <si>
+    <t>1049372051</t>
+  </si>
+  <si>
+    <t>MILENA ALEJANDRA GARCIA PRIETO</t>
+  </si>
+  <si>
+    <t>3229120724</t>
+  </si>
+  <si>
+    <t>52359085</t>
+  </si>
+  <si>
+    <t>WEIMAR JULIAN RODRIGUEZ DIAZ</t>
+  </si>
+  <si>
+    <t>3229120726</t>
+  </si>
+  <si>
+    <t>1003488824</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA COTAMO SANCHEZ</t>
+  </si>
+  <si>
+    <t>3229120731</t>
+  </si>
+  <si>
+    <t>1090508372</t>
+  </si>
+  <si>
+    <t>CLAUDIA PATRICIA HOLGUIN</t>
+  </si>
+  <si>
+    <t>3229120737</t>
+  </si>
+  <si>
+    <t>22466715</t>
+  </si>
+  <si>
+    <t>EDHISSON STIBENT ORJUELA TINOCO</t>
+  </si>
+  <si>
+    <t>3229120745</t>
+  </si>
+  <si>
+    <t>1022364520</t>
+  </si>
+  <si>
+    <t>SANTIAGO JACKSON CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>3229120732</t>
+  </si>
+  <si>
+    <t>1014303692</t>
+  </si>
+  <si>
+    <t>SOFIA HERNANDEZ CHUDT</t>
+  </si>
+  <si>
+    <t>3229120747</t>
+  </si>
+  <si>
+    <t>1053333864</t>
+  </si>
+  <si>
+    <t>ELENID JOHANNA RODRIGUEZ BAUTISTA</t>
+  </si>
+  <si>
+    <t>3229120748</t>
+  </si>
+  <si>
+    <t>63556857</t>
+  </si>
+  <si>
+    <t>FANCY MOSQUERA MOSQUERA</t>
+  </si>
+  <si>
+    <t>3229120750</t>
+  </si>
+  <si>
+    <t>35589748</t>
+  </si>
+  <si>
+    <t>DIEGO ANDRES SOCHA DIAZ</t>
+  </si>
+  <si>
+    <t>3229120755</t>
+  </si>
+  <si>
+    <t>80859441</t>
+  </si>
+  <si>
+    <t>MARIA MERCEDES RODRIGUEZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>3229120757</t>
+  </si>
+  <si>
+    <t>45743107</t>
+  </si>
+  <si>
+    <t>ANA GILMA VANEGAS AYALA</t>
+  </si>
+  <si>
+    <t>3229120758</t>
+  </si>
+  <si>
+    <t>24042079</t>
+  </si>
+  <si>
+    <t>HAROLD ALBERTO DOMINGUEZ SARMIENTO</t>
+  </si>
+  <si>
+    <t>3229120762</t>
+  </si>
+  <si>
+    <t>1116234182</t>
+  </si>
+  <si>
+    <t>NUMAEL ARIAS QUINTERO</t>
+  </si>
+  <si>
+    <t>3229120764</t>
+  </si>
+  <si>
+    <t>1062396970</t>
+  </si>
+  <si>
+    <t>ARMANDO TOBAR SALAZAR</t>
+  </si>
+  <si>
+    <t>3229120769</t>
+  </si>
+  <si>
+    <t>79534436</t>
+  </si>
+  <si>
+    <t>YHENKER JOSE BOLAÑO PABUENA</t>
+  </si>
+  <si>
+    <t>3229120779</t>
+  </si>
+  <si>
+    <t>1044936362</t>
+  </si>
+  <si>
+    <t>CARLOS ARBEY MARTINEZ</t>
+  </si>
+  <si>
+    <t>3229120787</t>
+  </si>
+  <si>
+    <t>79825632</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,6 +1616,10 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -115,18 +1670,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,22 +1988,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D183"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="31.95" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -455,38 +2014,2134 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
-        <v>3124879654</v>
-      </c>
-      <c r="C3" s="2">
-        <v>101135648</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3">
+        <v>3229127539</v>
+      </c>
+      <c r="C3">
+        <v>89392929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>3014458719</v>
-      </c>
-      <c r="C4">
-        <v>12329591</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>3229127539</v>
-      </c>
-      <c r="C5">
-        <v>89392929</v>
-      </c>
+      <c r="C4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" s="2"/>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="5"/>
+      <c r="B57" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="5"/>
+      <c r="B60" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D63" s="2"/>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="5"/>
+      <c r="B64" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="5"/>
+      <c r="B73" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D74" s="2"/>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D75" s="2"/>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D76" s="2"/>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D77" s="2"/>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="D79" s="2"/>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D81" s="2"/>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D82" s="2"/>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D83" s="2"/>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D84" s="2"/>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="5"/>
+      <c r="B85" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D85" s="2"/>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D86" s="2"/>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D87" s="2"/>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D88" s="2"/>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D89" s="2"/>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="5"/>
+      <c r="B90" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D90" s="2"/>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D91" s="2"/>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D92" s="2"/>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="5"/>
+      <c r="B93" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D93" s="2"/>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D94" s="2"/>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D95" s="2"/>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D96" s="2"/>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D97" s="2"/>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D98" s="2"/>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="5"/>
+      <c r="B99" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D99" s="2"/>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="5"/>
+      <c r="B100" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D100" s="2"/>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D101" s="2"/>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D102" s="2"/>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D103" s="2"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D104" s="2"/>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D105" s="2"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D106" s="2"/>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D107" s="2"/>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="D108" s="2"/>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D109" s="2"/>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D110" s="2"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="D111" s="2"/>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="5"/>
+      <c r="B112" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D112" s="2"/>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D113" s="2"/>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="D114" s="2"/>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D115" s="2"/>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="5"/>
+      <c r="B116" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D116" s="2"/>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D117" s="2"/>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D118" s="2"/>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D119" s="2"/>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D120" s="2"/>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D121" s="2"/>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="5"/>
+      <c r="B122" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D122" s="2"/>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D123" s="2"/>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="5"/>
+      <c r="B124" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D124" s="2"/>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D125" s="2"/>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="D126" s="2"/>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D127" s="2"/>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D128" s="2"/>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="D129" s="2"/>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D130" s="2"/>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D131" s="2"/>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D132" s="2"/>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="D133" s="2"/>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="D134" s="2"/>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D135" s="2"/>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="D136" s="2"/>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="D137" s="2"/>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="D138" s="2"/>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="D139" s="2"/>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="D140" s="2"/>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="D141" s="2"/>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="5"/>
+      <c r="B142" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="D142" s="2"/>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="D144" s="2"/>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D145" s="2"/>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="D146" s="2"/>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="D147" s="2"/>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="D148" s="2"/>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="D149" s="2"/>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="5"/>
+      <c r="B150" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="D150" s="2"/>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D151" s="2"/>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D152" s="2"/>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D153" s="2"/>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="D154" s="2"/>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="D155" s="2"/>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="D156" s="2"/>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="D157" s="2"/>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="D158" s="2"/>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="D159" s="2"/>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D160" s="2"/>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D161" s="2"/>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="D162" s="2"/>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="5"/>
+      <c r="B163" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="D163" s="2"/>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="D164" s="2"/>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="D165" s="2"/>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="D166" s="2"/>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="D167" s="2"/>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="D168" s="2"/>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="D169" s="2"/>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="D170" s="2"/>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D171" s="2"/>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="D172" s="2"/>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="D173" s="2"/>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="D174" s="2"/>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D175" s="2"/>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="D176" s="2"/>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="D177" s="2"/>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="D178" s="2"/>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="D179" s="2"/>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="D180" s="2"/>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="D181" s="2"/>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D182" s="2"/>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="D183" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
